--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{760AF24A-595D-472C-8F34-A9CD6477D319}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373BD7D9-BA04-49A9-82D0-0ABB9E534E26}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,12 @@
   </si>
   <si>
     <t>Gave my PEL CA and it went very well.</t>
+  </si>
+  <si>
+    <t>Attended Confrence in SDMA.</t>
+  </si>
+  <si>
+    <t>I accompanied my friend to the hospital for his appointment.</t>
   </si>
 </sst>
 </file>
@@ -2048,48 +2054,96 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>130</v>
+      </c>
+      <c r="D27" s="14">
+        <v>90</v>
+      </c>
+      <c r="E27" s="14">
+        <v>130</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+        <v>250</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B28" s="14">
+        <v>540</v>
+      </c>
+      <c r="C28" s="14">
+        <v>150</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>120</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>100</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{373BD7D9-BA04-49A9-82D0-0ABB9E534E26}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAEA1F25-E246-4029-8814-CFBBF4FE9FDA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>I accompanied my friend to the hospital for his appointment.</t>
+  </si>
+  <si>
+    <t>Prepared for my CA.</t>
   </si>
 </sst>
 </file>
@@ -2146,26 +2149,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B29" s="14">
+        <v>540</v>
+      </c>
+      <c r="C29" s="14">
+        <v>150</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>180</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="339" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAEA1F25-E246-4029-8814-CFBBF4FE9FDA}"/>
+  <xr:revisionPtr revIDLastSave="352" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33707630-A8D4-4CFC-BA37-C73729184455}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Prepared for my CA.</t>
+  </si>
+  <si>
+    <t>Gave my networking ca and that went very well and after college went to play football match.</t>
   </si>
 </sst>
 </file>
@@ -2194,27 +2197,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B30" s="14">
+        <v>500</v>
+      </c>
+      <c r="C30" s="14">
+        <v>180</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>150</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="14">
+        <v>150</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="352" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33707630-A8D4-4CFC-BA37-C73729184455}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B0B102-A2CB-4468-9AB5-E7214B998185}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Gave my networking ca and that went very well and after college went to play football match.</t>
+  </si>
+  <si>
+    <t>Felt sleepy all day.</t>
   </si>
 </sst>
 </file>
@@ -2244,26 +2247,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B31" s="14">
+        <v>450</v>
+      </c>
+      <c r="C31" s="14">
+        <v>150</v>
+      </c>
+      <c r="D31" s="14">
+        <v>60</v>
+      </c>
+      <c r="E31" s="14">
+        <v>130</v>
+      </c>
+      <c r="F31" s="14">
+        <v>350</v>
+      </c>
+      <c r="G31" s="14">
+        <v>7</v>
+      </c>
+      <c r="H31" s="14">
+        <v>150</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B0B102-A2CB-4468-9AB5-E7214B998185}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC55E386-F354-4091-88AC-D03AC017EED2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,12 @@
   </si>
   <si>
     <t>Felt sleepy all day.</t>
+  </si>
+  <si>
+    <t>Attended freshers party.</t>
+  </si>
+  <si>
+    <t>overall day was good.</t>
   </si>
 </sst>
 </file>
@@ -2293,48 +2299,96 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B32" s="14">
+        <v>480</v>
+      </c>
+      <c r="C32" s="14">
+        <v>180</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60</v>
+      </c>
+      <c r="E32" s="14">
+        <v>180</v>
+      </c>
+      <c r="F32" s="14">
+        <v>200</v>
+      </c>
+      <c r="G32" s="14">
+        <v>4</v>
+      </c>
+      <c r="H32" s="14">
+        <v>150</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B33" s="14">
+        <v>500</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>30</v>
+      </c>
+      <c r="E33" s="14">
+        <v>120</v>
+      </c>
+      <c r="F33" s="14">
+        <v>150</v>
+      </c>
+      <c r="G33" s="14">
+        <v>3</v>
+      </c>
+      <c r="H33" s="14">
+        <v>130</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC55E386-F354-4091-88AC-D03AC017EED2}"/>
+  <xr:revisionPtr revIDLastSave="401" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{061D2615-5762-4956-BF0A-83D0EA5E9AAC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>overall day was good.</t>
+  </si>
+  <si>
+    <t>Gave my dbms CA that went pretty well also accompanied my friend to the hospital after classes.</t>
   </si>
 </sst>
 </file>
@@ -2390,27 +2393,51 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>60</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>170</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="401" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{061D2615-5762-4956-BF0A-83D0EA5E9AAC}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4A35F47-1DC1-48AA-877C-00F4DE089D09}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>Gave my dbms CA that went pretty well also accompanied my friend to the hospital after classes.</t>
+  </si>
+  <si>
+    <t>Stayed inside the room for whole day and went to play football.</t>
   </si>
 </sst>
 </file>
@@ -2439,27 +2442,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B35" s="14">
+        <v>600</v>
+      </c>
+      <c r="C35" s="14">
+        <v>180</v>
+      </c>
+      <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
+        <v>180</v>
+      </c>
+      <c r="F35" s="14">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14">
+        <v>0</v>
+      </c>
+      <c r="H35" s="14">
+        <v>90</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4A35F47-1DC1-48AA-877C-00F4DE089D09}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E5874E6-8779-497E-9E26-04E27773FC6E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2488,27 +2488,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B36" s="14">
+        <v>600</v>
+      </c>
+      <c r="C36" s="14">
+        <v>200</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>90</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>160</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E5874E6-8779-497E-9E26-04E27773FC6E}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2CD5479-239E-4937-A33D-7719880D0533}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Stayed inside the room for whole day and went to play football.</t>
+  </si>
+  <si>
+    <t>Played football tournament in college and then prepared for python CA.</t>
   </si>
 </sst>
 </file>
@@ -2534,27 +2537,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B37" s="14">
+        <v>360</v>
+      </c>
+      <c r="C37" s="14">
+        <v>200</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>120</v>
+      </c>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2CD5479-239E-4937-A33D-7719880D0533}"/>
+  <xr:revisionPtr revIDLastSave="453" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7102553-3F4D-4533-BFF7-D63812AA1F5A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>Played football tournament in college and then prepared for python CA.</t>
+  </si>
+  <si>
+    <t>Played FSL semifinal and then gave my python CA.</t>
   </si>
 </sst>
 </file>
@@ -2583,27 +2586,51 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B38" s="14">
+        <v>450</v>
+      </c>
+      <c r="C38" s="14">
+        <v>300</v>
+      </c>
+      <c r="D38" s="14">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>120</v>
+      </c>
+      <c r="G38" s="14">
+        <v>2</v>
+      </c>
+      <c r="H38" s="14">
+        <v>140</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="453" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7102553-3F4D-4533-BFF7-D63812AA1F5A}"/>
+  <xr:revisionPtr revIDLastSave="468" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973BA422-E3A5-4F49-AD71-E59AC937A746}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Played FSL semifinal and then gave my python CA.</t>
+  </si>
+  <si>
+    <t>Nothing new happened same routine.</t>
   </si>
 </sst>
 </file>
@@ -2632,27 +2635,51 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B39" s="14">
+        <v>500</v>
+      </c>
+      <c r="C39" s="14">
+        <v>120</v>
+      </c>
+      <c r="D39" s="14">
+        <v>150</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>200</v>
+      </c>
+      <c r="G39" s="14">
+        <v>4</v>
+      </c>
+      <c r="H39" s="14">
+        <v>165</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>245</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{973BA422-E3A5-4F49-AD71-E59AC937A746}"/>
+  <xr:revisionPtr revIDLastSave="480" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B93E7E-AB51-4FC0-903C-A89173C195B4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>Nothing new happened same routine.</t>
+  </si>
+  <si>
+    <t>Nothing productive happened.</t>
   </si>
 </sst>
 </file>
@@ -2682,26 +2685,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B40" s="14">
+        <v>430</v>
+      </c>
+      <c r="C40" s="14">
+        <v>150</v>
+      </c>
+      <c r="D40" s="14">
+        <v>90</v>
+      </c>
+      <c r="E40" s="14">
+        <v>100</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>140</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="480" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6B93E7E-AB51-4FC0-903C-A89173C195B4}"/>
+  <xr:revisionPtr revIDLastSave="494" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{844E27A4-B71A-4E16-AC62-A2AAD514DEA4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>Nothing productive happened.</t>
+  </si>
+  <si>
+    <t>Day goal accomplished.</t>
   </si>
 </sst>
 </file>
@@ -2701,21 +2704,21 @@
         <v>100</v>
       </c>
       <c r="F40" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G40" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H40" s="14">
         <v>140</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>1260</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>60</v>
@@ -2731,26 +2734,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B41" s="14">
+        <v>460</v>
+      </c>
+      <c r="C41" s="14">
+        <v>160</v>
+      </c>
+      <c r="D41" s="14">
+        <v>30</v>
+      </c>
+      <c r="E41" s="14">
+        <v>150</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>180</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="494" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{844E27A4-B71A-4E16-AC62-A2AAD514DEA4}"/>
+  <xr:revisionPtr revIDLastSave="509" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC8CF60-0732-4956-8A02-9235A8A4B3AD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Day goal accomplished.</t>
+  </si>
+  <si>
+    <t>Gave analytical CA and went to play FSL final.</t>
   </si>
 </sst>
 </file>
@@ -2779,27 +2782,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B42" s="14">
+        <v>580</v>
+      </c>
+      <c r="C42" s="14">
+        <v>240</v>
+      </c>
+      <c r="D42" s="14">
+        <v>0</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>100</v>
+      </c>
+      <c r="G42" s="14">
+        <v>2</v>
+      </c>
+      <c r="H42" s="14">
+        <v>200</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="509" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC8CF60-0732-4956-8A02-9235A8A4B3AD}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C896FB36-B691-437C-BF4F-5F8CDF688750}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,12 +250,6 @@
     <t>Tried solving different dsa problems</t>
   </si>
   <si>
-    <t>Productive</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
     <t>Solved some important questions and enjoyed playing football.</t>
   </si>
   <si>
@@ -344,6 +338,9 @@
   </si>
   <si>
     <t>Gave analytical CA and went to play FSL final.</t>
+  </si>
+  <si>
+    <t>Slept for whole day.</t>
   </si>
 </sst>
 </file>
@@ -1528,16 +1525,16 @@
         <v>210</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>60</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1574,7 +1571,7 @@
         <v>210</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="L15" s="16" t="s">
         <v>60</v>
@@ -1583,7 +1580,7 @@
         <v>61</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1620,7 +1617,7 @@
         <v>300</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="L16" s="16" t="s">
         <v>50</v>
@@ -1629,7 +1626,7 @@
         <v>56</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1669,13 +1666,13 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1721,7 +1718,7 @@
         <v>61</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1761,13 +1758,13 @@
         <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1813,7 +1810,7 @@
         <v>56</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1850,7 +1847,7 @@
         <v>360</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>65</v>
@@ -1859,7 +1856,7 @@
         <v>56</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1896,7 +1893,7 @@
         <v>210</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>50</v>
@@ -1905,7 +1902,7 @@
         <v>61</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1951,7 +1948,7 @@
         <v>61</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1997,7 +1994,7 @@
         <v>61</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2043,7 +2040,7 @@
         <v>61</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2089,7 +2086,7 @@
         <v>57</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2135,7 +2132,7 @@
         <v>61</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2172,7 +2169,7 @@
         <v>410</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>60</v>
@@ -2181,7 +2178,7 @@
         <v>61</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2227,7 +2224,7 @@
         <v>61</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2273,7 +2270,7 @@
         <v>61</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2313,13 +2310,13 @@
         <v>57</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2356,7 +2353,7 @@
         <v>190</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>50</v>
@@ -2365,7 +2362,7 @@
         <v>56</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2402,7 +2399,7 @@
         <v>510</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L33" s="16" t="s">
         <v>50</v>
@@ -2411,7 +2408,7 @@
         <v>61</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2451,13 +2448,13 @@
         <v>60</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M34" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2503,7 +2500,7 @@
         <v>61</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2549,7 +2546,7 @@
         <v>61</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2595,7 +2592,7 @@
         <v>61</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2641,7 +2638,7 @@
         <v>57</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2687,7 +2684,7 @@
         <v>61</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2727,13 +2724,13 @@
         <v>60</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M40" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2779,7 +2776,7 @@
         <v>56</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2825,30 +2822,54 @@
         <v>57</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B43" s="14">
+        <v>630</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>60</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>200</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C896FB36-B691-437C-BF4F-5F8CDF688750}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6531EB1A-3120-4237-B28B-68C58997D41B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Slept for whole day.</t>
+  </si>
+  <si>
+    <t>Daily goals accomplished.</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1340,7 @@
         <v>1320</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I10="","",1440-I10)</f>
         <v>120</v>
       </c>
       <c r="K10" s="16" t="s">
@@ -2872,70 +2875,142 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>180</v>
+      </c>
+      <c r="D44" s="14">
+        <v>50</v>
+      </c>
+      <c r="E44" s="14">
+        <v>140</v>
+      </c>
+      <c r="F44" s="14">
+        <v>150</v>
+      </c>
+      <c r="G44" s="14">
+        <v>3</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B45" s="14">
+        <v>430</v>
+      </c>
+      <c r="C45" s="14">
+        <v>120</v>
+      </c>
+      <c r="D45" s="14">
+        <v>60</v>
+      </c>
+      <c r="E45" s="14">
+        <v>130</v>
+      </c>
+      <c r="F45" s="14">
+        <v>350</v>
+      </c>
+      <c r="G45" s="14">
+        <v>7</v>
+      </c>
+      <c r="H45" s="14">
+        <v>160</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>160</v>
+      </c>
+      <c r="D46" s="14">
+        <v>90</v>
+      </c>
+      <c r="E46" s="14">
+        <v>180</v>
+      </c>
+      <c r="F46" s="14">
+        <v>200</v>
+      </c>
+      <c r="G46" s="14">
+        <v>4</v>
+      </c>
+      <c r="H46" s="14">
+        <v>150</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6531EB1A-3120-4237-B28B-68C58997D41B}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6209CD6-7F37-4922-B888-98B9E00F1B0E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>Daily goals accomplished.</t>
+  </si>
+  <si>
+    <t>Worked on python project.</t>
   </si>
 </sst>
 </file>
@@ -3013,26 +3016,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B47" s="14">
+        <v>400</v>
+      </c>
+      <c r="C47" s="14">
+        <v>140</v>
+      </c>
+      <c r="D47" s="14">
+        <v>100</v>
+      </c>
+      <c r="E47" s="14">
+        <v>160</v>
+      </c>
+      <c r="F47" s="14">
+        <v>300</v>
+      </c>
+      <c r="G47" s="14">
+        <v>6</v>
+      </c>
+      <c r="H47" s="14">
+        <v>190</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>150</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6209CD6-7F37-4922-B888-98B9E00F1B0E}"/>
+  <xr:revisionPtr revIDLastSave="589" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57E15C20-4FCE-4BB2-9060-E12C048FB92C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Worked on python project.</t>
+  </si>
+  <si>
+    <t>Gave my ca2 of dbms</t>
   </si>
 </sst>
 </file>
@@ -3062,26 +3065,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46198</v>
+      </c>
+      <c r="B48" s="14">
+        <v>410</v>
+      </c>
+      <c r="C48" s="14">
+        <v>150</v>
+      </c>
+      <c r="D48" s="14">
+        <v>90</v>
+      </c>
+      <c r="E48" s="14">
+        <v>170</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>200</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="589" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57E15C20-4FCE-4BB2-9060-E12C048FB92C}"/>
+  <xr:revisionPtr revIDLastSave="631" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B44E74-ECE4-48E7-811D-89F655AB2F2B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>Gave my ca2 of dbms</t>
+  </si>
+  <si>
+    <t>same routine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protest </t>
   </si>
 </sst>
 </file>
@@ -3066,7 +3072,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13">
-        <v>46198</v>
+        <v>46290</v>
       </c>
       <c r="B48" s="14">
         <v>410</v>
@@ -3111,70 +3117,142 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B49" s="14">
+        <v>600</v>
+      </c>
+      <c r="C49" s="14">
+        <v>130</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>150</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>150</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B50" s="14">
+        <v>550</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>150</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B51" s="14">
+        <v>440</v>
+      </c>
+      <c r="C51" s="14">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>160</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="631" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B44E74-ECE4-48E7-811D-89F655AB2F2B}"/>
+  <xr:revisionPtr revIDLastSave="655" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF1194A2-E0DF-40C8-BA9A-7D8B055865CE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,12 @@
   </si>
   <si>
     <t xml:space="preserve">protest </t>
+  </si>
+  <si>
+    <t>travelled back to home</t>
+  </si>
+  <si>
+    <t>reached hone</t>
   </si>
 </sst>
 </file>
@@ -3255,48 +3261,96 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B52" s="14">
+        <v>400</v>
+      </c>
+      <c r="C52" s="14">
+        <v>0</v>
+      </c>
+      <c r="D52" s="14">
+        <v>0</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>150</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>890</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B53" s="14">
+        <v>400</v>
+      </c>
+      <c r="C53" s="14">
+        <v>0</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>180</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>860</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="655" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF1194A2-E0DF-40C8-BA9A-7D8B055865CE}"/>
+  <xr:revisionPtr revIDLastSave="667" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB96B0B8-EF27-438D-B39C-628E5A2CF97D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>reached hone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spent time with my parents </t>
   </si>
 </sst>
 </file>
@@ -3353,26 +3356,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B54" s="14">
+        <v>500</v>
+      </c>
+      <c r="C54" s="14">
+        <v>180</v>
+      </c>
+      <c r="D54" s="14">
+        <v>60</v>
+      </c>
+      <c r="E54" s="14">
+        <v>150</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>150</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="667" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB96B0B8-EF27-438D-B39C-628E5A2CF97D}"/>
+  <xr:revisionPtr revIDLastSave="679" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A157DEDD-3FFE-4BDF-AB11-D92819D0FF51}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t xml:space="preserve">spent time with my parents </t>
+  </si>
+  <si>
+    <t>enjoyed with my friends</t>
   </si>
 </sst>
 </file>
@@ -3402,26 +3405,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B55" s="14">
+        <v>550</v>
+      </c>
+      <c r="C55" s="14">
+        <v>160</v>
+      </c>
+      <c r="D55" s="14">
+        <v>60</v>
+      </c>
+      <c r="E55" s="14">
+        <v>120</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>180</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="679" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A157DEDD-3FFE-4BDF-AB11-D92819D0FF51}"/>
+  <xr:revisionPtr revIDLastSave="692" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024DE2FE-2F0C-4F5E-9C13-0061CFBC785A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>enjoyed with my friends</t>
+  </si>
+  <si>
+    <t>stayed at home</t>
   </si>
 </sst>
 </file>
@@ -3451,26 +3454,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B56" s="14">
+        <v>530</v>
+      </c>
+      <c r="C56" s="14">
+        <v>170</v>
+      </c>
+      <c r="D56" s="14">
+        <v>90</v>
+      </c>
+      <c r="E56" s="14">
+        <v>160</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>150</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="692" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024DE2FE-2F0C-4F5E-9C13-0061CFBC785A}"/>
+  <xr:revisionPtr revIDLastSave="717" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D216E598-3F9E-46F5-86C7-C590D0AADE1A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,12 @@
   </si>
   <si>
     <t>stayed at home</t>
+  </si>
+  <si>
+    <t>enjoyed at home</t>
+  </si>
+  <si>
+    <t>gave online classes</t>
   </si>
 </sst>
 </file>
@@ -3500,48 +3506,96 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B57" s="14">
+        <v>500</v>
+      </c>
+      <c r="C57" s="14">
+        <v>170</v>
+      </c>
+      <c r="D57" s="14">
+        <v>90</v>
+      </c>
+      <c r="E57" s="14">
+        <v>180</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>140</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B58" s="14">
+        <v>500</v>
+      </c>
+      <c r="C58" s="14">
+        <v>180</v>
+      </c>
+      <c r="D58" s="14">
+        <v>60</v>
+      </c>
+      <c r="E58" s="14">
+        <v>180</v>
+      </c>
+      <c r="F58" s="14">
+        <v>3</v>
+      </c>
+      <c r="G58" s="14">
+        <v>150</v>
+      </c>
+      <c r="H58" s="14">
+        <v>120</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1043</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>397</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="717" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D216E598-3F9E-46F5-86C7-C590D0AADE1A}"/>
+  <xr:revisionPtr revIDLastSave="763" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6374C9E7-41C2-478A-A443-729FCFCD4F00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,15 +235,9 @@
     <t>Very Satisfied</t>
   </si>
   <si>
-    <t>Moderate</t>
-  </si>
-  <si>
     <t>Overall day was productive.</t>
   </si>
   <si>
-    <t>Best</t>
-  </si>
-  <si>
     <t>Felt tired after classes</t>
   </si>
   <si>
@@ -377,6 +371,12 @@
   </si>
   <si>
     <t>gave online classes</t>
+  </si>
+  <si>
+    <t>online class</t>
+  </si>
+  <si>
+    <t>nothing new</t>
   </si>
 </sst>
 </file>
@@ -1429,10 +1429,10 @@
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>66</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1469,7 +1469,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L12" s="16" t="s">
         <v>65</v>
@@ -1478,7 +1478,7 @@
         <v>56</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1515,7 +1515,7 @@
         <v>120</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>50</v>
@@ -1524,7 +1524,7 @@
         <v>61</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1561,16 +1561,16 @@
         <v>210</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1616,7 +1616,7 @@
         <v>61</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1662,7 +1662,7 @@
         <v>56</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -1702,13 +1702,13 @@
         <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1754,7 +1754,7 @@
         <v>61</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1794,13 +1794,13 @@
         <v>49</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M19" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1846,7 +1846,7 @@
         <v>56</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1883,7 +1883,7 @@
         <v>360</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>65</v>
@@ -1892,7 +1892,7 @@
         <v>56</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1929,7 +1929,7 @@
         <v>210</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>50</v>
@@ -1938,7 +1938,7 @@
         <v>61</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1984,7 +1984,7 @@
         <v>61</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2030,7 +2030,7 @@
         <v>61</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2076,7 +2076,7 @@
         <v>61</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2122,7 +2122,7 @@
         <v>57</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2168,7 +2168,7 @@
         <v>61</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2205,7 +2205,7 @@
         <v>410</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>60</v>
@@ -2214,7 +2214,7 @@
         <v>61</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2260,7 +2260,7 @@
         <v>61</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2306,7 +2306,7 @@
         <v>61</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2346,13 +2346,13 @@
         <v>57</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2389,7 +2389,7 @@
         <v>190</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>50</v>
@@ -2398,7 +2398,7 @@
         <v>56</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2435,7 +2435,7 @@
         <v>510</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L33" s="16" t="s">
         <v>50</v>
@@ -2444,7 +2444,7 @@
         <v>61</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2484,13 +2484,13 @@
         <v>60</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M34" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2536,7 +2536,7 @@
         <v>61</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2582,7 +2582,7 @@
         <v>61</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2628,7 +2628,7 @@
         <v>61</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2674,7 +2674,7 @@
         <v>57</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2720,7 +2720,7 @@
         <v>61</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2760,13 +2760,13 @@
         <v>60</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M40" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2812,7 +2812,7 @@
         <v>56</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2858,7 +2858,7 @@
         <v>57</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2904,7 +2904,7 @@
         <v>57</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2950,7 +2950,7 @@
         <v>61</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -2987,7 +2987,7 @@
         <v>190</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L45" s="16" t="s">
         <v>65</v>
@@ -2996,7 +2996,7 @@
         <v>56</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -3042,7 +3042,7 @@
         <v>56</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -3088,7 +3088,7 @@
         <v>61</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -3134,7 +3134,7 @@
         <v>61</v>
       </c>
       <c r="N48" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -3180,7 +3180,7 @@
         <v>61</v>
       </c>
       <c r="N49" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -3220,13 +3220,13 @@
         <v>57</v>
       </c>
       <c r="L50" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M50" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N50" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -3272,7 +3272,7 @@
         <v>61</v>
       </c>
       <c r="N51" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -3318,7 +3318,7 @@
         <v>61</v>
       </c>
       <c r="N52" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3364,7 +3364,7 @@
         <v>61</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -3410,7 +3410,7 @@
         <v>56</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -3456,7 +3456,7 @@
         <v>61</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -3502,7 +3502,7 @@
         <v>61</v>
       </c>
       <c r="N56" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -3548,7 +3548,7 @@
         <v>56</v>
       </c>
       <c r="N57" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -3568,21 +3568,21 @@
         <v>180</v>
       </c>
       <c r="F58" s="14">
+        <v>150</v>
+      </c>
+      <c r="G58" s="14">
         <v>3</v>
-      </c>
-      <c r="G58" s="14">
-        <v>150</v>
       </c>
       <c r="H58" s="14">
         <v>120</v>
       </c>
       <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v>1043</v>
+        <v>1190</v>
       </c>
       <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v>397</v>
+        <v>250</v>
       </c>
       <c r="K58" s="16" t="s">
         <v>49</v>
@@ -3594,74 +3594,146 @@
         <v>61</v>
       </c>
       <c r="N58" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B59" s="14">
+        <v>480</v>
+      </c>
+      <c r="C59" s="14">
+        <v>150</v>
+      </c>
+      <c r="D59" s="14">
+        <v>90</v>
+      </c>
+      <c r="E59" s="14">
+        <v>120</v>
+      </c>
+      <c r="F59" s="14">
+        <v>350</v>
+      </c>
+      <c r="G59" s="14">
+        <v>7</v>
+      </c>
+      <c r="H59" s="14">
+        <v>110</v>
+      </c>
+      <c r="I59" s="15">
+        <f t="shared" si="0"/>
+        <v>1300</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B60" s="14">
+        <v>450</v>
+      </c>
+      <c r="C60" s="14">
+        <v>160</v>
+      </c>
+      <c r="D60" s="14">
+        <v>90</v>
+      </c>
+      <c r="E60" s="14">
+        <v>150</v>
+      </c>
+      <c r="F60" s="14">
+        <v>200</v>
+      </c>
+      <c r="G60" s="14">
+        <v>4</v>
+      </c>
+      <c r="H60" s="14">
+        <v>150</v>
+      </c>
+      <c r="I60" s="15">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="J60" s="15">
+        <f t="shared" si="1"/>
+        <v>240</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B61" s="14">
+        <v>460</v>
+      </c>
+      <c r="C61" s="14">
+        <v>180</v>
+      </c>
+      <c r="D61" s="14">
+        <v>100</v>
+      </c>
+      <c r="E61" s="14">
+        <v>200</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>180</v>
+      </c>
+      <c r="I61" s="15">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J61" s="15">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N61" s="17" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="763" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6374C9E7-41C2-478A-A443-729FCFCD4F00}"/>
+  <xr:revisionPtr revIDLastSave="788" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF6EA3F-F2E8-4573-B5D6-A036F635A67E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>nothing new</t>
+  </si>
+  <si>
+    <t>started prepration for mid term</t>
+  </si>
+  <si>
+    <t>preprations for midterm</t>
   </si>
 </sst>
 </file>
@@ -3736,48 +3742,96 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B62" s="14">
+        <v>480</v>
+      </c>
+      <c r="C62" s="14">
+        <v>180</v>
+      </c>
+      <c r="D62" s="14">
+        <v>200</v>
+      </c>
+      <c r="E62" s="14">
+        <v>90</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>240</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B63" s="14">
+        <v>500</v>
+      </c>
+      <c r="C63" s="14">
+        <v>200</v>
+      </c>
+      <c r="D63" s="14">
+        <v>220</v>
+      </c>
+      <c r="E63" s="14">
+        <v>100</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>220</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="788" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF6EA3F-F2E8-4573-B5D6-A036F635A67E}"/>
+  <xr:revisionPtr revIDLastSave="833" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C350E29-8354-4907-AAA8-3763409A8D6E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,12 @@
   </si>
   <si>
     <t>preprations for midterm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> travelling</t>
+  </si>
+  <si>
+    <t>midterm exam started</t>
   </si>
 </sst>
 </file>
@@ -3798,10 +3804,10 @@
         <v>200</v>
       </c>
       <c r="D63" s="14">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="E63" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F63" s="14">
         <v>0</v>
@@ -3814,11 +3820,11 @@
       </c>
       <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v>1240</v>
+        <v>1360</v>
       </c>
       <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="K63" s="16" t="s">
         <v>77</v>
@@ -3834,70 +3840,142 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B64" s="14">
+        <v>510</v>
+      </c>
+      <c r="C64" s="14">
+        <v>0</v>
+      </c>
+      <c r="D64" s="14">
+        <v>0</v>
+      </c>
+      <c r="E64" s="14">
+        <v>0</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>190</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B65" s="14">
+        <v>500</v>
+      </c>
+      <c r="C65" s="14">
+        <v>160</v>
+      </c>
+      <c r="D65" s="14">
+        <v>300</v>
+      </c>
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>150</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B66" s="14">
+        <v>500</v>
+      </c>
+      <c r="C66" s="14">
+        <v>150</v>
+      </c>
+      <c r="D66" s="14">
+        <v>320</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>180</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="833" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C350E29-8354-4907-AAA8-3763409A8D6E}"/>
+  <xr:revisionPtr revIDLastSave="871" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{931A1900-C465-43F7-BFB2-299B329DBC13}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>midterm exam started</t>
+  </si>
+  <si>
+    <t>midterm exam</t>
+  </si>
+  <si>
+    <t>holiday</t>
   </si>
 </sst>
 </file>
@@ -3974,74 +3980,146 @@
         <v>56</v>
       </c>
       <c r="N66" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B67" s="14">
+        <v>530</v>
+      </c>
+      <c r="C67" s="14">
+        <v>120</v>
+      </c>
+      <c r="D67" s="14">
+        <v>350</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>170</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B68" s="14">
+        <v>540</v>
+      </c>
+      <c r="C68" s="14">
+        <v>150</v>
+      </c>
+      <c r="D68" s="14">
+        <v>380</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>190</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+      <c r="A69" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B69" s="14">
+        <v>530</v>
+      </c>
+      <c r="C69" s="14">
+        <v>120</v>
+      </c>
+      <c r="D69" s="14">
+        <v>360</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>150</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="871" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{931A1900-C465-43F7-BFB2-299B329DBC13}"/>
+  <xr:revisionPtr revIDLastSave="909" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3154001-5129-4B3A-8432-2B7757433F67}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="123">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -395,6 +395,15 @@
   </si>
   <si>
     <t>holiday</t>
+  </si>
+  <si>
+    <t>exam</t>
+  </si>
+  <si>
+    <t>enjoyed Sunday</t>
+  </si>
+  <si>
+    <t>classes started</t>
   </si>
 </sst>
 </file>
@@ -4122,70 +4131,142 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+      <c r="A70" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B70" s="14">
+        <v>530</v>
+      </c>
+      <c r="C70" s="14">
+        <v>150</v>
+      </c>
+      <c r="D70" s="14">
+        <v>380</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>155</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>1215</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
+        <v>225</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+      <c r="A71" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B71" s="14">
+        <v>560</v>
+      </c>
+      <c r="C71" s="14">
+        <v>200</v>
+      </c>
+      <c r="D71" s="14">
+        <v>0</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>170</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="13"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="A72" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B72" s="14">
+        <v>480</v>
+      </c>
+      <c r="C72" s="14">
+        <v>180</v>
+      </c>
+      <c r="D72" s="14">
+        <v>160</v>
+      </c>
+      <c r="E72" s="14">
+        <v>180</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>160</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="909" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3154001-5129-4B3A-8432-2B7757433F67}"/>
+  <xr:revisionPtr revIDLastSave="952" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F723A74-B2C2-4109-9733-D3FCEDC599DE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="124">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -404,6 +404,9 @@
   </si>
   <si>
     <t>classes started</t>
+  </si>
+  <si>
+    <t>dussehra</t>
   </si>
 </sst>
 </file>
@@ -4239,21 +4242,21 @@
         <v>180</v>
       </c>
       <c r="F72" s="14">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G72" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H72" s="14">
         <v>160</v>
       </c>
       <c r="I72" s="15">
         <f t="shared" si="2"/>
-        <v>1160</v>
+        <v>1310</v>
       </c>
       <c r="J72" s="15">
         <f t="shared" si="3"/>
-        <v>280</v>
+        <v>130</v>
       </c>
       <c r="K72" s="16" t="s">
         <v>60</v>
@@ -4269,70 +4272,142 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="13"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
+      <c r="A73" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B73" s="14">
+        <v>540</v>
+      </c>
+      <c r="C73" s="14">
+        <v>190</v>
+      </c>
+      <c r="D73" s="14">
+        <v>60</v>
+      </c>
+      <c r="E73" s="14">
+        <v>230</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>180</v>
+      </c>
+      <c r="I73" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J73" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="13"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
+      <c r="A74" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B74" s="14">
+        <v>480</v>
+      </c>
+      <c r="C74" s="14">
+        <v>160</v>
+      </c>
+      <c r="D74" s="14">
+        <v>50</v>
+      </c>
+      <c r="E74" s="14">
+        <v>180</v>
+      </c>
+      <c r="F74" s="14">
+        <v>250</v>
+      </c>
+      <c r="G74" s="14">
+        <v>4</v>
+      </c>
+      <c r="H74" s="14">
+        <v>260</v>
+      </c>
+      <c r="I74" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J74" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="13"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
+      <c r="A75" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B75" s="14">
+        <v>490</v>
+      </c>
+      <c r="C75" s="14">
+        <v>180</v>
+      </c>
+      <c r="D75" s="14">
+        <v>60</v>
+      </c>
+      <c r="E75" s="14">
+        <v>220</v>
+      </c>
+      <c r="F75" s="14">
+        <v>300</v>
+      </c>
+      <c r="G75" s="14">
+        <v>6</v>
+      </c>
+      <c r="H75" s="14">
+        <v>180</v>
+      </c>
+      <c r="I75" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J75" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="952" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F723A74-B2C2-4109-9733-D3FCEDC599DE}"/>
+  <xr:revisionPtr revIDLastSave="989" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CF682AC-AD90-4AB5-BB54-3E0B88EC79FB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="127">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -407,6 +407,15 @@
   </si>
   <si>
     <t>dussehra</t>
+  </si>
+  <si>
+    <t>football meeting</t>
+  </si>
+  <si>
+    <t>studied dsa</t>
+  </si>
+  <si>
+    <t>went out with my friends</t>
   </si>
 </sst>
 </file>
@@ -4410,70 +4419,142 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="13"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
+      <c r="A76" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B76" s="14">
+        <v>480</v>
+      </c>
+      <c r="C76" s="14">
+        <v>200</v>
+      </c>
+      <c r="D76" s="14">
+        <v>90</v>
+      </c>
+      <c r="E76" s="14">
+        <v>200</v>
+      </c>
+      <c r="F76" s="14">
+        <v>300</v>
+      </c>
+      <c r="G76" s="14">
+        <v>6</v>
+      </c>
+      <c r="H76" s="14">
+        <v>160</v>
+      </c>
+      <c r="I76" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J76" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="13"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
+      <c r="A77" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B77" s="14">
+        <v>530</v>
+      </c>
+      <c r="C77" s="14">
+        <v>200</v>
+      </c>
+      <c r="D77" s="14">
+        <v>120</v>
+      </c>
+      <c r="E77" s="14">
+        <v>200</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>200</v>
+      </c>
+      <c r="I77" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J77" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="13"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
+      <c r="A78" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B78" s="14">
+        <v>530</v>
+      </c>
+      <c r="C78" s="14">
+        <v>160</v>
+      </c>
+      <c r="D78" s="14">
+        <v>100</v>
+      </c>
+      <c r="E78" s="14">
+        <v>150</v>
+      </c>
+      <c r="F78" s="14">
+        <v>0</v>
+      </c>
+      <c r="G78" s="14">
+        <v>0</v>
+      </c>
+      <c r="H78" s="14">
+        <v>380</v>
+      </c>
+      <c r="I78" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J78" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>

--- a/12607000.xlsx
+++ b/12607000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9fd775d52677595d/Desktop/PYTHON Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="989" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CF682AC-AD90-4AB5-BB54-3E0B88EC79FB}"/>
+  <xr:revisionPtr revIDLastSave="1028" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F009BE14-C236-4EAF-841B-1873921E7C08}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="612" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="128">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>went out with my friends</t>
+  </si>
+  <si>
+    <t>solved problems</t>
   </si>
 </sst>
 </file>
@@ -4557,70 +4560,142 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="13"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+      <c r="A79" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B79" s="14">
+        <v>550</v>
+      </c>
+      <c r="C79" s="14">
+        <v>180</v>
+      </c>
+      <c r="D79" s="14">
+        <v>60</v>
+      </c>
+      <c r="E79" s="14">
+        <v>150</v>
+      </c>
+      <c r="F79" s="14">
+        <v>0</v>
+      </c>
+      <c r="G79" s="14">
+        <v>0</v>
+      </c>
+      <c r="H79" s="14">
+        <v>250</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="13"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+      <c r="A80" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B80" s="14">
+        <v>480</v>
+      </c>
+      <c r="C80" s="14">
+        <v>180</v>
+      </c>
+      <c r="D80" s="14">
+        <v>60</v>
+      </c>
+      <c r="E80" s="14">
+        <v>160</v>
+      </c>
+      <c r="F80" s="14">
+        <v>250</v>
+      </c>
+      <c r="G80" s="14">
+        <v>5</v>
+      </c>
+      <c r="H80" s="14">
+        <v>250</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+      <c r="A81" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B81" s="14">
+        <v>470</v>
+      </c>
+      <c r="C81" s="14">
+        <v>200</v>
+      </c>
+      <c r="D81" s="14">
+        <v>70</v>
+      </c>
+      <c r="E81" s="14">
+        <v>180</v>
+      </c>
+      <c r="F81" s="14">
+        <v>200</v>
+      </c>
+      <c r="G81" s="14">
+        <v>4</v>
+      </c>
+      <c r="H81" s="14">
+        <v>270</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>
